--- a/Bao gia.xlsx
+++ b/Bao gia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\700976\source\github\UploadFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A69EE9E-B8AF-432F-870A-56F42A466CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03940732-73D1-4A88-9A1A-F4D9DA6CED3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A86C3EC9-6D50-448D-8FAE-1556633BC104}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
   <si>
     <t>Chức năng</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Khác</t>
   </si>
   <si>
-    <t>Chi phí bên thứ 3</t>
-  </si>
-  <si>
     <t>Xem, thêm, sửa, xóa</t>
   </si>
   <si>
@@ -156,6 +153,18 @@
   </si>
   <si>
     <t>Xem</t>
+  </si>
+  <si>
+    <t>Chi phí bên thứ 3 (khoảng 250K-300K/ năm)</t>
+  </si>
+  <si>
+    <t>Chi phí bên thứ 3 (khoảng 250K-300K/ tháng)</t>
+  </si>
+  <si>
+    <t>Chi phí bên thứ 3 ( khoảng 500K/ 1 tháng)</t>
+  </si>
+  <si>
+    <t>Chi phí bên thứ 3 (tùy vào đuôi, từ 200K-400K, gia hạn theo năm khoảng 400K-500K/ 1 năm)</t>
   </si>
 </sst>
 </file>
@@ -280,9 +289,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -301,17 +315,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
@@ -654,55 +664,56 @@
     <col min="3" max="3" width="5.140625" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" customWidth="1"/>
     <col min="5" max="5" width="25.140625" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="81.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>36</v>
+      <c r="H4" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1">
@@ -712,107 +723,107 @@
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" s="1">
         <v>1000</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1">
         <v>6</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1">
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>8</v>
       </c>
@@ -820,261 +831,261 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
+      <c r="B14" s="9"/>
       <c r="C14" s="1">
         <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="1">
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="1">
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
+      <c r="B17" s="9"/>
       <c r="C17" s="1">
         <v>13</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
+      <c r="B18" s="9"/>
       <c r="C18" s="1">
         <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
+      <c r="B19" s="9"/>
       <c r="C19" s="1">
         <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
+      <c r="B20" s="9"/>
       <c r="C20" s="1">
         <v>16</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="1">
         <v>17</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
+      <c r="B22" s="9"/>
       <c r="C22" s="1">
         <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="9"/>
       <c r="C23" s="1">
         <v>19</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F23" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
+      <c r="B24" s="9"/>
       <c r="C24" s="1">
         <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="1">
+        <v>9</v>
+      </c>
+      <c r="F25" s="13">
         <v>500</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="1">
         <v>22</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="3"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="1">
         <v>23</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="3"/>
+      <c r="B28" s="6"/>
       <c r="C28" s="1">
         <v>24</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="4"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="1">
         <v>25</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1089,15 +1100,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100464EAFD93F199941AEF21E1CD7793124" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58d1039e41a4cb93cd4a6ee7116d6881">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="489e31e2-434f-4b61-9bdf-770bf5ae2e16" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="da89e2e7b2ba2031744592081261f6ce" ns3:_="">
     <xsd:import namespace="489e31e2-434f-4b61-9bdf-770bf5ae2e16"/>
@@ -1285,6 +1287,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1294,14 +1305,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5FFDB71-3497-456F-8D68-02BCF139C72D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF4899E7-46F0-45A9-8669-42B508CDF7D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1315,6 +1318,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5FFDB71-3497-456F-8D68-02BCF139C72D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
